--- a/main/StructureDefinition-bc-confidentiality-extension.xlsx
+++ b/main/StructureDefinition-bc-confidentiality-extension.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-30T21:39:06+00:00</t>
+    <t>2026-04-01T23:28:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1238,7 +1238,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="5" hidden="true">
+    <row r="5">
       <c r="A5" t="s" s="2">
         <v>98</v>
       </c>
@@ -1654,7 +1654,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="9" hidden="true">
+    <row r="9">
       <c r="A9" t="s" s="2">
         <v>113</v>
       </c>
@@ -1755,7 +1755,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>122</v>
       </c>
@@ -1860,7 +1860,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>127</v>
       </c>
@@ -1965,7 +1965,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>132</v>
       </c>
@@ -2280,12 +2280,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AK14">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
